--- a/stories/arbres/ATOM-TMP.SEM.002-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Prune est dans la cuisine avec maman. Sur le frigo, il y a un calendrier. Des aimants de couleurs. Maman dit : demain c'est lundi. Lundi, mardi, jeudi, vendredi : Prune va à l'école. Mercredi, Prune reste à la maison. Elle joue avec maman. Samedi, Prune reste aussi à la maison. Dimanche encore. Maman dit : samedi et dimanche, c'est le week-end. Prune pose l'aimant mercredi. Pas d'école ce jour-là. Elle dessine. Plus tard, Prune pose l'aimant samedi. Puis l'aimant dimanche. Même leçon, autre jour. Maman dit : mercredi, samedi, dimanche, on est à la maison.</t>
+          <t>Prune est dans la cuisine avec maman. Sur le frigo, il y a un calendrier. Des aimants de couleurs. Demain c'est lundi. Lundi, mardi, jeudi, vendredi : Prune va à l'école. Mercredi, Prune reste à la maison. Elle joue avec maman. Samedi, Prune reste aussi à la maison. Dimanche encore. Samedi et dimanche, c'est le week-end. Prune pose l'aimant mercredi. Pas d'école ce jour-là. Elle dessine. Plus tard, Prune pose l'aimant samedi. Puis l'aimant dimanche. Même leçon, autre jour. Mercredi, samedi, dimanche, on est à la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Prune est dans la cuisine avec maman. Sur le frigo, il y a un calendrier. Des aimants de couleurs.
+maman|Demain c'est lundi. Lundi, mardi, jeudi, vendredi : Prune va à l'école. Mercredi, Prune reste à la maison. Elle joue avec maman. Samedi, Prune reste aussi à la maison. Dimanche encore.
+maman|Samedi et dimanche, c'est le week-end.
+narrateur|Prune pose l'aimant mercredi. Pas d'école ce jour-là. Elle dessine. Plus tard, Prune pose l'aimant samedi. Puis l'aimant dimanche. Même leçon, autre jour.
+maman|Mercredi, samedi, dimanche, on est à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Prune est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Prune a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Prune range ses crayons. Maman prépare le goûter.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 maman|Mercredi, samedi, dimanche, on est à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Prune est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Prune a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Prune range ses crayons. Maman prépare le goûter.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.002-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prune nomme mercredi et le week-end</t>
+          <t>Le sel et la coquille</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino veut un coquillage entier. Mercredi, le seau revient avec du sable. Le week-end, à la plage, une coquille entière tient dans sa paume.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Prune est dans la cuisine avec maman. Sur le frigo, il y a un calendrier. Des aimants de couleurs. Demain c'est lundi. Lundi, mardi, jeudi, vendredi : Prune va à l'école. Mercredi, Prune reste à la maison. Elle joue avec maman. Samedi, Prune reste aussi à la maison. Dimanche encore. Samedi et dimanche, c'est le week-end. Prune pose l'aimant mercredi. Pas d'école ce jour-là. Elle dessine. Plus tard, Prune pose l'aimant samedi. Puis l'aimant dimanche. Même leçon, autre jour. Mercredi, samedi, dimanche, on est à la maison.</t>
+          <t>Le sel colle déjà aux vitres. Le vent sent le goémon, un peu fort. Le sable crisse sous la première marche. C'est mercredi, Nino. Pas d'école. On va au bord ? Oui. La petite plage. Je veux un coquillage. On cherche. Nino porte un seau bleu. Le seau tape sa jambe, toc toc. En ce moment, il creuse près d'une vague. L'eau revient trop vite. Le trou se referme. Il part. La mer reprend le sable. On recule un peu ? Oui. Il recule. Ses chaussures ont un liseré blanc de sel. Il fouille avec les doigts. Un éclat cassé, rien d'entier. C'est cassé. Mercredi, on a le temps court. Samedi, on reviendra. La grande plage ? La grande. Samedi et dimanche, c'est le week-end. Pas d'école. Pas d'école. Comme mercredi. Nino verse le sable dans le seau. Ça fait chh, puis plus rien. Pas de coquille. Du sable pour attendre. Tu veux rincer tes mains ? Elles collent. L'eau froide pique un peu. Le sel reste dans les plis. On rentre. Le seau vient. Le seau vient. Une mouette crie, très haut. Nino lève le menton. Elle a vu la mer. Moi aussi. Samedi, tu verras plus loin. Le seau est lourd de sable mouillé. Une goutte tombe sur le bois de la marche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Prune est dans la cuisine avec maman. Sur le frigo, il y a un calendrier. Des aimants de couleurs. Maman dit : demain c'est lundi. Lundi, mardi, jeudi, vendredi : Prune va à l'école. &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;, Prune reste à la maison. Elle joue avec maman. Samedi, Prune reste aussi à la maison. Dimanche encore. Maman dit : samedi et dimanche, c'est le week-end. Prune pose l'aimant mercredi. Pas d'école ce jour-là. Elle dessine. Plus tard, Prune pose l'aimant samedi. Puis l'aimant dimanche. Même leçon, autre jour. Maman dit : mercredi, samedi, dimanche, on est à la maison.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sel colle déjà aux vitres. Le vent sent le goémon, un peu fort. Le sable crisse sous la première marche. C'est mercredi, Nino. Pas d'école. On va au bord ? Oui. La petite plage. Je veux un coquillage. On cherche. Nino porte un seau bleu. Le seau tape sa jambe, toc toc. En ce moment, il creuse près d'une vague. L'eau revient trop vite. Le trou se referme. Il part. La mer reprend le sable. On recule un peu ? Oui. Il recule. Ses chaussures ont un liseré blanc de sel. Il fouille avec les doigts. Un éclat cassé, rien d'entier. C'est cassé. Mercredi, on a le temps court. Samedi, on reviendra. La grande plage ? La grande. Samedi et dimanche, c'est le week-end. Pas d'école. Pas d'école. Comme mercredi. Nino verse le sable dans le seau. Ça fait chh, puis plus rien. Pas de coquille. Du sable pour attendre. Tu veux rincer tes mains ? Elles collent. L'eau froide pique un peu. Le sel reste dans les plis. On rentre. Le seau vient. Le seau vient. Une mouette crie, très haut. Nino lève le menton. Elle a vu la mer. Moi aussi. Samedi, tu verras plus loin. Le seau est lourd de sable mouillé. Une goutte tombe sur le bois de la marche.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Prune est dans la cuisine avec maman. Sur le frigo, il y a un calendrier. Des aimants de couleurs.
-maman|Demain c'est lundi. Lundi, mardi, jeudi, vendredi : Prune va à l'école. Mercredi, Prune reste à la maison. Elle joue avec maman. Samedi, Prune reste aussi à la maison. Dimanche encore.
+          <t>narrateur|Le sel colle déjà aux vitres.
+narrateur|Le vent sent le goémon, un peu fort.
+narrateur|Le sable crisse sous la première marche.
+maman|C'est mercredi, Nino.
+maman|Pas d'école.
+enfant-m|On va au bord ?
+maman|Oui.
+maman|La petite plage.
+enfant-m|Je veux un coquillage.
+maman|On cherche.
+narrateur|Nino porte un seau bleu.
+narrateur|Le seau tape sa jambe, toc toc.
+narrateur|En ce moment, il creuse près d'une vague.
+narrateur|L'eau revient trop vite.
+narrateur|Le trou se referme.
+enfant-m|Il part.
+maman|La mer reprend le sable.
+maman|On recule un peu ?
+enfant-m|Oui.
+narrateur|Il recule.
+narrateur|Ses chaussures ont un liseré blanc de sel.
+narrateur|Il fouille avec les doigts.
+narrateur|Un éclat cassé, rien d'entier.
+enfant-m|C'est cassé.
+maman|Mercredi, on a le temps court.
+maman|Samedi, on reviendra.
+enfant-m|La grande plage ?
+maman|La grande.
 maman|Samedi et dimanche, c'est le week-end.
-narrateur|Prune pose l'aimant mercredi. Pas d'école ce jour-là. Elle dessine. Plus tard, Prune pose l'aimant samedi. Puis l'aimant dimanche. Même leçon, autre jour.
-maman|Mercredi, samedi, dimanche, on est à la maison.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-m|Pas d'école.
+maman|Pas d'école.
+maman|Comme mercredi.
+narrateur|Nino verse le sable dans le seau.
+narrateur|Ça fait chh, puis plus rien.
+enfant-m|Pas de coquille.
+maman|Du sable pour attendre.
+maman|Tu veux rincer tes mains ?
+enfant-m|Elles collent.
+narrateur|L'eau froide pique un peu.
+narrateur|Le sel reste dans les plis.
+maman|On rentre.
+enfant-m|Le seau vient.
+maman|Le seau vient.
+narrateur|Une mouette crie, très haut.
+narrateur|Nino lève le menton.
+maman|Elle a vu la mer.
+enfant-m|Moi aussi.
+maman|Samedi, tu verras plus loin.
+narrateur|Le seau est lourd de sable mouillé.
+narrateur|Une goutte tombe sur le bois de la marche.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1400,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Prune est à la maison le mercredi. Quels autres jours aussi ?</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Prune est à la maison le &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;. Quels autres jours aussi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1364,7 +1420,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>week-end | weekend | samedi | dimanche | le week-end</t>
+          <t>week-end | weekend | samedi | dimanche | le week-end | mercredi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1421,14 +1477,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1560,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Prune est à la maison le mercredi. Quels autres jours aussi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Quels autres jours, comme mercredi, sans l'école ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Prune a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
+          <t>Nino pose le seau près des chaussures. Samedi. Dimanche. Oui. C'est le week-end. On cherchera encore. Une entière. Une entière. Il touche le sable du seau. C'est froid, un peu lourd. Mercredi a donné le sable. Le week-end donnera la coquille. J'attends. Tu as cherché. Bravo. Tu as reculé devant la vague ? Oui, maman. Le sel sèche en petits cristaux blancs.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Prune a nommé &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;. Elle a nommé samedi et dimanche. C'est le week-end.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino pose le seau près des chaussures. Samedi. Dimanche. Oui. C'est le week-end. On cherchera encore. Une entière. Une entière. Il touche le sable du seau. C'est froid, un peu lourd. Mercredi a donné le sable. Le week-end donnera la coquille. J'attends. Tu as cherché. Bravo. Tu as reculé devant la vague ? Oui, maman. Le sel sèche en petits cristaux blancs.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1600,7 +1655,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,10 +1731,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Prune a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino pose le seau près des chaussures.
+enfant-m|Samedi.
+enfant-m|Dimanche.
+maman|Oui.
+maman|C'est le week-end.
+maman|On cherchera encore.
+enfant-m|Une entière.
+maman|Une entière.
+narrateur|Il touche le sable du seau.
+narrateur|C'est froid, un peu lourd.
+maman|Mercredi a donné le sable.
+maman|Le week-end donnera la coquille.
+enfant-m|J'attends.
+maman|Tu as cherché.
+maman|Bravo.
+maman|Tu as reculé devant la vague ?
+enfant-m|Oui, maman.
+narrateur|Le sel sèche en petits cristaux blancs.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,12 +1775,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Prune range ses crayons. Maman prépare le goûter.</t>
+          <t>Samedi, la grande plage est plus large. Le vent pousse une odeur de goémon doux. Je cherche. Près de la laisse de mer. Nino s'agenouille. Une coquille entière, rose au bord. Elle est entière ! Tu l'as. Il la pose dans le seau, sur le sable. Elle ne se casse pas. Dimanche, on l'écoutera à la maison. La mer dedans ? La mer dedans. C'est le week-end. Merci, maman. Merci d'avoir attendu samedi. La coquille est tiède dans la paume. Le sel brille encore sur le bord rose.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Prune range ses crayons. Maman prépare le goûter.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Samedi, la grande plage est plus large. Le vent pousse une odeur de goémon doux. Je cherche. Près de la laisse de mer. Nino s'agenouille. Une coquille entière, rose au bord. Elle est entière ! Tu l'as. Il la pose dans le seau, sur le sable. Elle ne se casse pas. Dimanche, on l'écoutera à la maison. La mer dedans ? La mer dedans. C'est le week-end. Merci, maman. Merci d'avoir attendu samedi. La coquille est tiède dans la paume. Le sel brille encore sur le bord rose.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1772,7 +1843,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1840,10 +1911,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Prune range ses crayons. Maman prépare le goûter.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Samedi, la grande plage est plus large.
+narrateur|Le vent pousse une odeur de goémon doux.
+enfant-m|Je cherche.
+maman|Près de la laisse de mer.
+narrateur|Nino s'agenouille.
+narrateur|Une coquille entière, rose au bord.
+enfant-m|Elle est entière !
+maman|Tu l'as.
+narrateur|Il la pose dans le seau, sur le sable.
+narrateur|Elle ne se casse pas.
+maman|Dimanche, on l'écoutera à la maison.
+enfant-m|La mer dedans ?
+maman|La mer dedans.
+maman|C'est le week-end.
+enfant-m|Merci, maman.
+maman|Merci d'avoir attendu samedi.
+narrateur|La coquille est tiède dans la paume.
+narrateur|Le sel brille encore sur le bord rose.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je l'ai. Elle est entière. La coquille tient au creux de la main. Un souffle de mer reste dans le trou. Le seau bleu garde un peu de sable clair.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je l'ai. Elle est entière. La coquille tient au creux de la main. Un souffle de mer reste dans le trou. Le seau bleu garde un peu de sable clair.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1936,7 +2023,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2008,10 +2095,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Je l'ai.
+maman|Elle est entière.
+narrateur|La coquille tient au creux de la main.
+narrateur|Un souffle de mer reste dans le trou.
+narrateur|Le seau bleu garde un peu de sable clair.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>petite plage mercredi, grande plage le week-end</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prune, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
